--- a/base de canciones/canciones_sin_letras_repetidas.xlsx
+++ b/base de canciones/canciones_sin_letras_repetidas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="868">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="875">
   <si>
     <t>año</t>
   </si>
@@ -12463,72 +12463,79 @@
     <t>https://genius.com/search?q=Natti%20Natasha%20Me%20Gusta</t>
   </si>
   <si>
-    <t xml:space="preserve">[Intro]_x000D_
-Ella, ella, ella_x000D_
-Ah-ah-ah-ahh_x000D_
+    <t>_x000D_
+[Intro]_x000D_
+(Yo sé que la' noche' no son sola para mí)_x000D_
+Natti Na', Natti Na'_x000D_
+_x000D_
+[Pre-Estribillo]_x000D_
+Me-Me-Me-Me gusta_x000D_
+Lo' beso' prohibido', lo que hay escondido', me gusta_x000D_
+Que me hablen bajito, así respiraito', me gusta_x000D_
+Me gusta donde haya peligro, donde haya delirio, me gusta_x000D_
+E' malo, pero es que me gusta_x000D_
+_x000D_
+[Estribillo]_x000D_
+Y sí, yo sé que la' noche' no son sola' para mí_x000D_
+Que tú tienes a alguien pero me quieres a mí_x000D_
+Yo sé que me piensas cuando estoy lejos de ti_x000D_
+Y si me preguntan digo que nunca te vi_x000D_
 _x000D_
 [Verso 1]_x000D_
-Préndelo y apágalo_x000D_
-Ven dímelo, ay yo ya ví_x000D_
-Es obvio que tú mil cosas quieres hacer_x000D_
-Y cuando te hablan de mí_x000D_
-Conmigo te las imaginas_x000D_
-Ya sé, es obvio que tú_x000D_
-Mil cosas quieres hacer_x000D_
-Y cuando te hablan de mí_x000D_
-Conmigo te las imaginas_x000D_
-_x000D_
-[Coro]_x000D_
-Si yo apago la luz, tú la quieres prender_x000D_
-Que yo sé que tú prefieres tocar lo que quieres ver_x000D_
-Si ya entendimos todas las señales_x000D_
-Hoy voy a hacerte hasta lo que no sabes_x000D_
-Porque yo sé que tú prefieres tocar lo que puedes ver_x000D_
-Así que vente pa' la oscuridad (Baby, baby)_x000D_
-Así que vente pa' la oscuridad (Baby, baby)_x000D_
+No somos amigos, pero tenemos privilegio'_x000D_
+No' vemos a escondida' y eso que no hay nada serio_x000D_
+Pa' qué tener un compromiso_x000D_
+Si dice que te ama pero en su cama a mi fue la que quiso_x000D_
+Lo' bueno' buscan lo malo y lo' malo' buscan lo bueno_x000D_
+Podemo' pecar pero sin arrepentimiento_x000D_
+Lo ajeno es prohibido y como quiera yo lo tengo_x000D_
+Repetimos siempre que puedo_x000D_
+_x000D_
+[Pre-Estribillo]_x000D_
+Porque me gusta (Ah, ah)_x000D_
+Lo' beso' prohibido', lo que hay escondido', me gusta_x000D_
+Que me hablen bajito, así respiraito', me gusta_x000D_
+Me gusta donde haya peligro, donde haya delirio, me gusta_x000D_
+E' malo, pero es que me gusta_x000D_
+_x000D_
+[Estribillo]_x000D_
+Y sí, yo sé que la' noche' no son sola' para mí_x000D_
+Que tú tienes a alguien pero me quieres a mí_x000D_
+Yo sé que me piensas cuando estoy lejos de ti_x000D_
+Y si me preguntan digo que nunca te vi_x000D_
+_x000D_
+[Post-Estribillo]_x000D_
+(Oh, oh, oh)_x000D_
+Que nunca te vi (Oh)_x000D_
+(Oh-oh, oh-oh)_x000D_
+(Oh, oh, oh)_x000D_
+(Yay, yay; ¡'cucha!)_x000D_
 _x000D_
 [Verso 2]_x000D_
-Casi que no, casi no caigo_x000D_
-Digo que no, pero siempre nos damos todo_x000D_
-Siempre terminamos dando todo_x000D_
-Pídeme lo que tú quiera'_x000D_
-Pídeme todo lo que tu cuerpo quiera_x000D_
-Pídeme lo que tú quiera'_x000D_
-Pídeme todo lo que tu cuerpo quiera_x000D_
-_x000D_
-[Coro]_x000D_
-Si yo apago la luz, tú la quieres prender_x000D_
-Que yo sé que tú prefieres tocar lo que quieres ver_x000D_
-Si ya entendimos todas las señales_x000D_
-Hoy voy a hacerte hasta lo que no sabes_x000D_
-Porque yo sé que tú prefieres tocar lo que puedes ver_x000D_
-Así que vente pa' la oscuridad (Baby, baby)_x000D_
-Así que vente pa' la oscuridad (Baby, baby)_x000D_
-_x000D_
-[Puente]_x000D_
-Tú prefieres toc–_x000D_
-Porque yo se que tú prefieres toc–_x000D_
-Porque yo se que tú prefieres toc–_x000D_
-Tú pre– prefieres ver_x000D_
-Es obvio que tú mil cosas quieres hacer_x000D_
-Y cuando te hablan de mí_x000D_
-Conmigo te las imaginas_x000D_
-[Coro]_x000D_
-Si yo apago la luz, tú la quieres prender_x000D_
-Que yo sé que tú prefieres tocar lo que quieres ver_x000D_
-Si ya entendimos todas las señales_x000D_
-Hoy voy a hacerte hasta lo que no sabes_x000D_
-Porque yo sé que tú prefieres tocar lo que puedes ver_x000D_
-Así que vente pa' la oscuridad_x000D_
-(Así que vente pa' la oscuridad)_x000D_
+En mi mano cae como pieza de dominó_x000D_
+Sin fajarme mucho, este juego lo domino_x000D_
+Porque te tengo bien loco_x000D_
+A-A ti te tengo loco_x000D_
+Te hackeo el formato cuando le das al link_x000D_
+Te robo la victoria cuando me bajo el pink_x000D_
+Así te pongo loco_x000D_
+Papi, te tengo loco_x000D_
+¡Ahí fue!_x000D_
+_x000D_
+[Estribillo]_x000D_
+Y sí, yo sé que la' noche' no son sola' para mí_x000D_
+Que tú tienes a alguien pero me quieres a mí_x000D_
+Yo sé que me piensas cuando estoy lejos de ti_x000D_
+Y si me preguntan digo que nunca te vi_x000D_
+_x000D_
+[Post-Estribillo]_x000D_
+(Oh, oh, oh)_x000D_
+Que nunca te vi (Oh)_x000D_
+(Oh-oh, oh-oh)_x000D_
+(Oh, oh, oh)_x000D_
 _x000D_
 [Outro]_x000D_
-Pídeme todo lo que tu cuerpo quiera_x000D_
-Pídeme todo lo que tu cuerpo quiera_x000D_
-Pídeme todo lo que tu cuerpo quiera_x000D_
-Pídeme todo lo que tu cuerpo quiera_x000D_
-_x000D_
-</t>
+(Que nunca te vi)</t>
   </si>
   <si>
     <t>No Me Acuerdo</t>
@@ -13820,77 +13827,91 @@
 </t>
   </si>
   <si>
-    <t>https://genius.com/search?q=Karol%20G%20Punto%20G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Intro]_x000D_
-(Ey, ey, ey)_x000D_
-_x000D_
-[Verso 1]_x000D_
-Sigue la pista, me vas a encontrar_x000D_
-Ya estás cerquita de mí (De mí)_x000D_
-Como acertijo en bola de cristal_x000D_
-Tú me quieres descubrir_x000D_
-_x000D_
-[Pre-Coro 1]_x000D_
-P-Para hasta la mitad_x000D_
-Sube el caminito_x000D_
-Sigue ahí, ahí_x000D_
-Dale, avanza un poco más_x000D_
-Pero si te pierdes, yo te voy a esperar_x000D_
-_x000D_
-[Coro]_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-_x000D_
-[Verso 2]_x000D_
-Casi, casi que te puedo ver_x000D_
-Sigue bien las instrucciones para que sepas qué hacer_x000D_
-Que estoy esperando por uno que me enamore_x000D_
-A la vieja escuela, que me mande flores_x000D_
-Quiero que me lleve al cine_x000D_
-Quiero que me robe un beso_x000D_
-Pero por la noche también se ponga travieso_x000D_
-Que ande por mi cama siempre sin pijama_x000D_
-Escuchando música todo el fin de semana_x000D_
-_x000D_
-[Pre-Coro 2]_x000D_
-Que sepa escoger, que sepa decidir_x000D_
-Si anda con Shakira, J-Lo o Karol G_x000D_
-Que me toque allá, que me toque ahí_x000D_
-Hasta que me encuentre espero ahí_x000D_
-_x000D_
-[Coro]_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-_x000D_
-[Verso 3]_x000D_
-Apaga la luz, que oscurito lo prefiero_x000D_
-Lo que quieres tú, yo ya lo pensé primero_x000D_
-Como Betty Boop, a todos los desespero_x000D_
-Yo decido a cuál boto y con cuál me quedo_x000D_
-Ya vi que anda buscando una rica mamacita que le baje_x000D_
-Y que el proceso le repita_x000D_
-Y sé que no ha encontrado una que se lo permita_x000D_
-Yo soy tu favorita, se te nota en la carita_x000D_
-_x000D_
-[Pre-Coro 2]_x000D_
-Que sepa escoger, que sepa decidir_x000D_
-Si anda con Shakira, J-Lo o Karol G_x000D_
-Que me toque allá, que me toque ahí_x000D_
-Hasta que me encuentre espero ahí_x000D_
-[Coro]_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-En el punto G_x000D_
-(En el punto G)_x000D_
+    <t>Secreto</t>
+  </si>
+  <si>
+    <t>Anuel AA &amp; Karol G</t>
+  </si>
+  <si>
+    <t>https://genius.com/Karol-g-and-anuel-aa-secreto-lyrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: Anuel AA]_x000D_
+Bebecita_x000D_
+Bebe-bebecita, uah_x000D_
+Bebecita_x000D_
+_x000D_
+[Coro: Anuel AA, Karol G &amp; Ambos]_x000D_
+Lo de nosotro' e' un secreto, que nadie se entere (Uah)_x000D_
+Baby, yo siempre me vengo contigo cuando tú te viene' (Uah)_x000D_
+Ante el mundo somos amigo' y lo hacemo' escondido' (Oh, oh, oh)_x000D_
+Tú y yo solo' en mi cama y Dios es el testigo (Oh, oh, oh)_x000D_
+Lo de nosotros es un secreto, pero siempre nos vemo' (No' vemo')_x000D_
+Y to' el mundo habla de nosotros, pero siempre nos comemos (Comemo')_x000D_
+Y tú me hiciste enloquecer, yeh (Oh-oh-oh, oh-oh)_x000D_
+Y contigo me siento bien, yeh (Oh-oh-oh, oh-oh, oh), ah_x000D_
+Y nadie nunca lo va saber (Bebé), que tú ere' mi mujer (Mi mujer)_x000D_
+Y nadie junto' nos quiere ver, pero no' vamo' a esconder_x000D_
+_x000D_
+[Verso 1: Anuel AA &amp; Karol G]_x000D_
+Yo te hago el amor bien rico_x000D_
+Y te aprieto la mano (La mano)_x000D_
+Bebé, ya son como la' cuatro y pico_x000D_
+Pero pa'l sexo es temprano (Temprano)_x000D_
+Baby, conmigo tú te sientes vivo, pero siempre no' matamo'_x000D_
+Lo' secretos siempre se saben, baby, tarde o temprano (Temprano)_x000D_
+_x000D_
+[Coro: Anuel AA, Karol G, Ambos]_x000D_
+Nuestro amor es un secreto, pero siempre nos vemos (Eh-eh)_x000D_
+Y to' el mundo habla de nosotros, pero siempre nos comemos (Eh-eh)_x000D_
+Y tú me hiciste enloquecer, yeh_x000D_
+Y contigo me siento bien, yeh_x000D_
+Y nadie nunca lo va a saber (Bebé), que yo soy tu mujer (Mujer)_x000D_
+Y contigo no me quieren ver (Eh-eh), pero nos vamo' a esconder (Eh, eh, eh)_x000D_
+_x000D_
+[Verso 2: Anuel AA &amp; Karol G]_x000D_
+Imposible el celibato, sin ti me mato_x000D_
+Y de tu cuerpo soy un tecato (-cato)_x000D_
+Bebé, tú ere' mía, yo no comparto (Uah)_x000D_
+Y siempre te rompo to'a en mi cuarto, bebé (Ey)_x000D_
+Imposible el celibato, sin ti me mato_x000D_
+Y tú ere' mío, yo no comparto_x000D_
+Hasta la muerte hicimo' un pacto (Uah)_x000D_
+Y siempre lo hacemo' rico en mi cuarto, bebé_x000D_
+Bebecita, bebecita (Babe; uah)_x000D_
+_x000D_
+[Coro: Anuel AA &amp; Karol G]_x000D_
+Lo de nosotro' e' un secreto, que nadie se entere (-tere, eh)_x000D_
+Baby, yo siempre me vengo contigo cuando tú te viene' (Eh, eh, eh)_x000D_
+Ante el mundo somos amigo' y lo hacemo' a escondido' (-dido')_x000D_
+Tú y yo solo en mi cama y Dios es el testigo (Testigo)_x000D_
+Lo de nosotros es un secreto, pero siempre nos vemo' (Nos vemo'; eh-eh)_x000D_
+Y to' el mundo habla de nosotros, pero siempre nos comemos (Comemo')_x000D_
+Y tú me hiciste enloquecer, yeh (Eh-eh)_x000D_
+Y contigo me siento bien, yeh_x000D_
+Y nadie nunca lo va a saber, que tú ere' mi mujer (Mujer)_x000D_
+Y contigo no me quieren ver (Bebé), pero nos vamo' a esconder_x000D_
+Ey, ah, ah (Oh-oh-oh-oh)_x000D_
+[Outro: Anuel AA &amp; Karol G]_x000D_
+(Real Hasta La Muerte, baby)_x000D_
+Dale, dale, ey_x000D_
+Baby (Real Hasta La Muerte, baby)_x000D_
+Dale, dale, ey, uah (Uah)_x000D_
+Karol G, uah_x000D_
+(Bebecita), Karol G, bebecita (Oh-oh-oh; uah, uah)_x000D_
+Mera, dime, EZ (Uah, uah; EZ who made the beat)_x000D_
+Lo' intocable', ¿oíste, bebé?_x000D_
+Eh, ah (Oh-oh-oh, oh-oh, oh)_x000D_
+Real Hasta La Muerte, bebecita (Eh, eh)_x000D_
+Bebecito (¡Brr!)_x000D_
+Uy, Anuel (Eh, eh)_x000D_
+Mera, dime, Frabian (Hmm, no)_x000D_
+Mera, dime, Prida (Ah, uah)_x000D_
+(Bebecita)_x000D_
+Mera, dime, EQ_x000D_
+(Bebe-bebecita; uah-uah, eh-eh)_x000D_
+Bebe-bebecita, ah-ah-ah-ah_x000D_
+Bebecita, ah-ah-ah-ah (Uah-uah, eh-eh)_x000D_
 </t>
   </si>
   <si>
@@ -14592,6 +14613,95 @@
 O-O-Ovy On The Drums_x000D_
 Papi, papi_x000D_
 </t>
+  </si>
+  <si>
+    <t>Relación</t>
+  </si>
+  <si>
+    <t>Sech</t>
+  </si>
+  <si>
+    <t>https://genius.com/Sech-relacion-lyrics</t>
+  </si>
+  <si>
+    <t>[Pre-Estribillo]_x000D_
+Ella siempre estaba cuando tú no estabas_x000D_
+Fue tanto dolor que ya no la mataba_x000D_
+Poco a poco ya no te necesitaba_x000D_
+Ella sonreía mientras lo enrolaba_x000D_
+Y tú (Tú, uh-uh-uh)_x000D_
+Diciendo que fue falta de actitud_x000D_
+Pero en esta relación hizo más que tú, yeh (Yeh-eh)_x000D_
+Y en un estado te manda a decir que_x000D_
+_x000D_
+[Estribillo]_x000D_
+Ahora todo cambió, le toca a ella (Le toca a ella)_x000D_
+Mari y una botella_x000D_
+Gracia' al maltrato se puso bella (Se puso bella)_x000D_
+Ahora tú la quiere' y no te quiere ella_x000D_
+Y ahora todo cambió, le toca a ella (Le toca a ella)_x000D_
+Mari y una botella_x000D_
+Gracia' al maltrato se puso bella (Se puso bella)_x000D_
+Ahora tú la quiere' y no te quiere ella_x000D_
+_x000D_
+[Verso 1]_x000D_
+Sí, ¡eh!_x000D_
+Cambió, cambió y tú estás' pagando (Yeah)_x000D_
+Se fue el balón y quiere seguir jugando (Come on)_x000D_
+Mientras lloraba, tú estaba' tomando_x000D_
+Ahora estás llamando y ella se está cambiando_x000D_
+Que va pa' la calle (Calle), sin dar detalle' (-talle')_x000D_
+Con ese traje yo dudo que ella falle_x000D_
+Siempre linda, con o sin maquillaje (Maquillaje)_x000D_
+Siempre en línea, automático el mensaje que (Mensaje que)_x000D_
+_x000D_
+[Estribillo]_x000D_
+Ahora todo cambió, le toca a ella (Le toca a ella)_x000D_
+Mari y una botella_x000D_
+Gracia' al maltrato se puso bella (Se puso bella)_x000D_
+Ahora tú la quiere' y no te quiere ella_x000D_
+Y ahora todo cambió, le toca a ella (Le toca a ella)_x000D_
+Mari y una botella_x000D_
+Gracia' al maltrato se puso bella (Se puso bella)_x000D_
+Ahora tú la quiere' y no te quiere ella_x000D_
+_x000D_
+[Verso 2]_x000D_
+Y ahora todo cambió, comenzó por su estado (-tado)_x000D_
+Ahora te toca esperarla sentado (Wuh)_x000D_
+Cambió de número, pa' que uste' ni piense en llamar (Ni piense)_x000D_
+Te toca extrañarla na' má'_x000D_
+Ya jugó otro número (Número)_x000D_
+Y también borró tu número (Número)_x000D_
+Prendió uno y te superó (Superó)_x000D_
+Le pusieron la canción y gritó: "Súbelo" (Súbelo)_x000D_
+_x000D_
+[Pre-Estribillo]_x000D_
+Ella siempre estaba cuando tú no estabas_x000D_
+Fue tanto dolor que ya no la mataba (Mataba)_x000D_
+Poco a poco ya no te necesitaba (-cesitaba)_x000D_
+Ella sonreía mientras lo enrolaba_x000D_
+Y tú (Tú, uh-uh-uh)_x000D_
+Diciendo que fue falta de actitud_x000D_
+Pero en esta relación hizo más que tú, yeh (Yeh-eh)_x000D_
+Y en un estado te manda a decir que_x000D_
+_x000D_
+[Estribillo]_x000D_
+Ahora todo cambió, le toca a ella (Le toca a ella)_x000D_
+Mari y una botella_x000D_
+Gracia' al maltrato se puso bella (Se puso bella)_x000D_
+Ahora tú la quiere' y no te quiere ella_x000D_
+Y ahora todo cambió, le toca a ella (Le toca a ella)_x000D_
+Mari y una botella_x000D_
+Gracia' al maltrato se puso bella (Se puso bella)_x000D_
+Ahora tú la quiere' y no te quiere ella_x000D_
+_x000D_
+[Outro]_x000D_
+Dímelo Flow_x000D_
+Slow Mike_x000D_
+Este es Sech_x000D_
+Rich Music_x000D_
+El Bloke_x000D_
+1964, bien</t>
   </si>
   <si>
     <t>Sigues Con Él</t>
@@ -16803,130 +16913,107 @@
 </t>
   </si>
   <si>
-    <t>BOBO</t>
-  </si>
-  <si>
-    <t>Mariah Angeliq, Bad Gyal y María Becerra</t>
-  </si>
-  <si>
-    <t>https://genius.com/search?q=Mariah%20Angeliq%2C%20Bad%20Gyal%20y%20Mar%C3%ADa%20Becerra%20BOBO</t>
-  </si>
-  <si>
-    <t>_x000D_
-Visualizaciones de la letra_x000D_
-22.055_x000D_
-BOBO (part. Bad Gyal y Maria Becerra)_x000D_
-Mariah Angeliq_x000D_
-_x000D_
-El Nuevo Orden_x000D_
-Yeah_x000D_
-It's Mariah, baby_x000D_
-Yeah_x000D_
-_x000D_
-Un bobo se piensa que es genial_x000D_
-Pero nunca llega a pasar_x000D_
-Siempre habla de lo que va a comprar_x000D_
-Y en el banco no tiene na'_x000D_
-_x000D_
-So, no, no quiero darte mi número (no quiero dártelo)_x000D_
-No quiero salir contigo, no_x000D_
-Tú no puede' estar conmigo, no_x000D_
-Ni siquiera ser mi amigo_x000D_
-_x000D_
-No, no quiero un bobo_x000D_
-Un bobo es alguien que jamá' me hará feli'_x000D_
-Porque no para de llamar, ni de textear_x000D_
-Siempre atrás de mí (ah)_x000D_
-_x000D_
-No quiero un bobo_x000D_
-Un bobo es alguien que jamá' me hará feli' (no quiero)_x000D_
-Porque no para de llamar, ni de textear (no quiero)_x000D_
-Siempre atrás de mí_x000D_
-_x000D_
-(Mariah, bitch)_x000D_
-Me dicen que doy frío y yo solo me río_x000D_
-No te enamore', que yo tengo el corazón vacío_x000D_
-A nadie le doy mi contacto, no ere' de lo' mío'_x000D_
-So deja tu jueguito y lo' truquito' porque yo_x000D_
-_x000D_
-No quiero darte mi número_x000D_
-No quiero salir contigo, no_x000D_
-Tú no puede' estar conmigo, no_x000D_
-Ni siquiera ser mi amigo_x000D_
-_x000D_
-No, no quiero un bobo_x000D_
-Un bobo es alguien que jamá' me hará feli'_x000D_
-Porque no para de llamar, ni de textear_x000D_
-Siempre atrás de mí (ah)_x000D_
-_x000D_
-No quiero un bobo (no quiero)_x000D_
-Un bobo es alguien que jamá' me hará feli' (no quiero)_x000D_
-Porque no para de llamar, ni de textear (no quiero)_x000D_
-Siempre atrás de mí (Bad Gyal)_x000D_
-_x000D_
-Este se ha crecido, cree que yo quiero un bobo_x000D_
-Una cena conmigo, la cuenta, te jodo_x000D_
-Las mejore' pareja' van codo con codo_x000D_
-No da' la talla, eso lo saben todo'_x000D_
-_x000D_
-Y tú me llama', y el DM, y el WhatsApp me lo explota'_x000D_
-Y di que coge un avión para venirse pa' Europa_x000D_
-Y si lo hiciera, yo a mí me llamarían loca_x000D_
-Si hay otro que me toca_x000D_
-_x000D_
-¿De dónde sacó mi teléfono?_x000D_
-Mana me interrogó y me presionó_x000D_
-Te juro, he intenta'o to' los método'_x000D_
-Que ere' bobo, no es un secreto_x000D_
-No es un hombre completo, no_x000D_
-_x000D_
-No, no quiero un bobo_x000D_
-Un bobo es un man que jamá' me hará feli'_x000D_
-Porque no para de llamar, ni de textear_x000D_
-Y siempre atrás de mí_x000D_
-_x000D_
-No quiero un bobo_x000D_
-Un bobo es un man que jamá' me hará feli'_x000D_
-¿Por qué no para de llamarme y de textear?_x000D_
-Siempre atrás de mí_x000D_
-_x000D_
-Ay, ¡qué pesa'o!_x000D_
-Creo que tú te volviste loco_x000D_
-Comentándome toda' la' foto'_x000D_
-_x000D_
-Engatusa'o_x000D_
-Sigue soñando que te toco_x000D_
-Pero do' vece' no me equivoco_x000D_
-(Ey, yeah)_x000D_
-_x000D_
-Stop, baby, nobody fucks with me_x000D_
-Te enamoraste desde el día en el que te di_x000D_
-Fuck, ¿no ve' que no te respondí?_x000D_
-Pasaste po' al la'o y ni te vi_x000D_
-_x000D_
-Yeah, yeah, ah_x000D_
-Sabe' que de toda' soy la más dura_x000D_
-Buena por fuera, por dentro oscura_x000D_
-Independiente_x000D_
-Yo tan fría y tú tan caliente_x000D_
-_x000D_
-No, no quiero un bobo_x000D_
-Un bobo es alguien que jamá' me hará feli'_x000D_
-Porque no para de llamar, ni de textear_x000D_
-Siempre atrás de mí_x000D_
-_x000D_
-No quiero un bobo_x000D_
-Un bobo e' alguien que jamá' me hará feli' (bobo)_x000D_
-Porque no para de llamar, ni de textear_x000D_
-Siempre atrás de mí_x000D_
-_x000D_
-(Atrás de mí)_x000D_
-Ey, don't sweat it_x000D_
-Dime lo desea_x000D_
-Lady, lady_x000D_
-Bad Gyal_x000D_
-Uh_x000D_
-It's Mariah, baby</t>
+    <t>Volví</t>
+  </si>
+  <si>
+    <t>Aventura &amp; Bad Bunny</t>
+  </si>
+  <si>
+    <t>Colaboración Hombres</t>
+  </si>
+  <si>
+    <t>https://genius.com/Aventura-and-bad-bunny-volvi-lyrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">_x000D_
+[Intro: Romeo Santos]_x000D_
+Dime por qué le tiras piedras a la luna_x000D_
+Tan ilógico como extraerme de tu piel_x000D_
+Después de Dios, soy tu todo, mujer_x000D_
+¿Qué tal te está yendo con él?_x000D_
+_x000D_
+[Coro: Romeo Santos &amp; Bad Bunny]_x000D_
+Yo sé que al final_x000D_
+A mí no me olvidas tan siquiera un poco_x000D_
+Al final, baby, tú extrañas cómo yo te toco_x000D_
+Recuerda, de tu cuerpo sé yo, mami_x000D_
+Cada rincón por dentro y por fuera_x000D_
+Dile que volví por ti (Yeh, yeh, yeh, yeh)_x000D_
+_x000D_
+[Verso 1: Bad Bunny &amp; Romeo Santos]_x000D_
+Yo soy ese tatuaje, mami, que no se te borra_x000D_
+Sin palomería', yo no bajo con cotorra_x000D_
+Dile al bobo ese que еn mí siempre e' quе tú piensa'_x000D_
+Que cuando él termina e' cuando tú apena' comienza'_x000D_
+Y ahí e', ahí e' cuando tú siente' la diferencia_x000D_
+Yo siempre te daba con consistencia_x000D_
+Dile que se retire, haga su diligencia_x000D_
+Porque volví por ti (Volví)_x000D_
+Pa' hacértelo bien rico como te gusta a ti_x000D_
+Ponte en cuatro y te la saco como lo hace Tatí'_x000D_
+Te montaste en la Jeepeta y no tenía' panty_x000D_
+So no te engañes_x000D_
+Que e' imposible que no me extrañe'_x000D_
+Lo nuestro e' de año', no hay forma de que se dañe_x000D_
+Con él ni suda', no hace falta ni que tú te bañe'_x000D_
+Despué' de lo' polvo' conmigo la' sábana' hay que botarla'_x000D_
+Toalla pa' la nena pa' secarla_x000D_
+No quiero a otra, tú ere' la que sabe sacarla_x000D_
+Hoy vine pa' rescatarla (So nasty)_x000D_
+_x000D_
+[Coro: Romeo Santos]_x000D_
+Yo sé que al final_x000D_
+A mí no me olvidas tan siquiera un poco_x000D_
+Al final, baby, tú extrañas cómo yo te toco_x000D_
+Recuerda, de tu cuerpo sé yo, mami_x000D_
+Cada rincón por dentro y por fuera_x000D_
+Dile que volví por ti, yeah_x000D_
+_x000D_
+[Verso 2: Romeo Santos &amp; Bad Bunny]_x000D_
+¿Cómo carajo ese palomo va a compararse conmigo?_x000D_
+Ni te conoce mientras yo soy tu delirio_x000D_
+Tengo la fecha escrita en el calendario_x000D_
+Si yo volví a Aventura, tú regresas a mi lado, baby_x000D_
+Que cuente las horas_x000D_
+Es su destino, tú y yo tenemo' historia_x000D_
+Para que él vea que el dinero no lo es todo_x000D_
+Te enamoré con mi lujuria, yo controlo_x000D_
+Tú sabes que ese tipo es temporal_x000D_
+Anda, arranca y dile_x000D_
+Tú despide de una vez a ese cabró— (Ey)_x000D_
+_x000D_
+[Puente: Bad Bunny &amp; Romeo Santos]_x000D_
+Porque volví por ti_x000D_
+Pa' hacértelo bien rico como te gusta a ti_x000D_
+Ponte en cuatro y te la saco como lo hace Tatí'_x000D_
+Te montaste en la Jeepeta y no tenía' panty_x000D_
+Porque volví, mami, por ti_x000D_
+Lo haces con él pero pensando en mí_x000D_
+Inconforme con ese infeliz_x000D_
+Hey, you end up with me_x000D_
+[Coro: Romeo Santos &amp; Bad Bunny]_x000D_
+Yo sé que al final_x000D_
+A mí no me olvida' tan siquiera un poco_x000D_
+Al final, baby, tú te mojas cuando yo te toco_x000D_
+Recuerda, de tu cuerpo sé yo, mami (Ey, ey)_x000D_
+Cada rincón por dentro y por fuera (Ey, ey, ey, ey)_x000D_
+Dile que volví por ti_x000D_
+_x000D_
+[Outro: Bad Bunny &amp; Romeo Santos, Ambos]_x000D_
+Bad Bunny, baby, bebé_x000D_
+Bad Bunny, baby, bebé_x000D_
+Te toca a ti, Romeo_x000D_
+Dile_x000D_
+Aventura_x000D_
+Tú ere' mía, bebé_x000D_
+Tú ere' mía, bebé_x000D_
+Vamo' a hacerlo otra ve'_x000D_
+Vamo' a hacerlo otra ve'_x000D_
+Tú ere' mía, bebé_x000D_
+Tú ere' mía, bebé_x000D_
+Vamo' a hacerlo otra ve'_x000D_
+Jaja, ey_x000D_
+</t>
   </si>
   <si>
     <t>Me Porto Bonito</t>
@@ -18154,79 +18241,106 @@
 </t>
   </si>
   <si>
-    <t>CANDY</t>
-  </si>
-  <si>
-    <t>https://genius.com/search?q=Rosal%C3%ADa%20CANDY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[Pre-Coro]_x000D_
-Vestí'a con F de Fendi_x000D_
-Bailando Plan B, la de "Candy"_x000D_
-Así tú te prendaste de mí_x000D_
-El día en que yo te conocí_x000D_
-_x000D_
-[Coro]_x000D_
-Sé que tú no me has olvida'o_x000D_
-No me has olvida'o, no me has olvida'o_x000D_
-Solo tú no me has olvida'o_x000D_
-No me has olvida'o, no me has olvida'o_x000D_
-_x000D_
-[Post-Coro]_x000D_
-Ya no te quiero como antes_x000D_
-Me rompiste, pero solo en parte'_x000D_
-Llevaba tu esclava para pensarte_x000D_
-Pero de olvidarte yo ya hice un arte_x000D_
-Más na', na', na', na', na', na'_x000D_
-No queda na', na', na', na', na'_x000D_
-Entre tú y yo, ya-ya-ya-ya_x000D_
-_x000D_
-[Verso]_x000D_
-Ya no me acuerdo de tu cara_x000D_
-La forma de tu cuerpo ni aunquе la pensara_x000D_
-Hay demasia'o que nos sеpara_x000D_
-La vida es bonita pero traicionera_x000D_
-_x000D_
-_x000D_
-[Pre-Coro]_x000D_
-Vestí'a con F de Fendi (Fendi, Fendi, Fendi)_x000D_
-Bailando Plan B, la de "Candy" (Candy, candy, candy)_x000D_
-Así tú te prendaste de mí (Eh, eh)_x000D_
-El día en que yo te conocí_x000D_
-_x000D_
-[Coro]_x000D_
-Pero tú no me has olvida'o_x000D_
-No me has olvida'o, no me has olvida'o_x000D_
-Solo tú no me has olvida'o_x000D_
-No me has olvida'o, no me has olvida'o_x000D_
-_x000D_
-[Post-Coro]_x000D_
-Na', na', na', na', na'_x000D_
-No queda na', na', na', na', na'_x000D_
-Entre tú y yo, ya-ya-ya-ya_x000D_
-Na', na', na', na', na'_x000D_
-No queda na', na', na', na', na'_x000D_
-Entre tú y yo, ya-ya-ya-ya_x000D_
-_x000D_
-[Pre-Coro]_x000D_
-Vestí'a con F de Fendi (Fendi, Fendi, Fendi)_x000D_
-Bailando Plan B, la de "Candy" (Candy, candy, candy)_x000D_
-Así tú te prendaste de mí (Eh, eh)_x000D_
-El día en que yo te conocí (El día en que yo te conocí)_x000D_
-Vestí'a con F de Fendi (Fendi, Fendi, Fendi)_x000D_
-Bailando Plan B, la de "Candy" (Candy, candy, candy)_x000D_
-Así tú te prendaste de mí (Eh, eh)_x000D_
-El día en que yo te conocí (Sí, sí, sí, sí)_x000D_
-[Coro]_x000D_
-Pero tú no me has olvida'o_x000D_
-No me has olvida'o, no me has olvida'o_x000D_
-Sólo tú no me has olvida'o_x000D_
-No me has olvida'o, no me has olvida'o_x000D_
-_x000D_
-[Outro]_x000D_
-Oh, oh_x000D_
-No, ah, ah_x000D_
-Mmm, mmm (No me has olvida'o)_x000D_
+    <t>Tití Me Preguntó</t>
+  </si>
+  <si>
+    <t>https://genius.com/Bad-bunny-titi-me-pregunto-lyrics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Intro: Bad Bunny]_x000D_
+Ey_x000D_
+_x000D_
+[Coro: Bad Bunny]_x000D_
+Tití me preguntó si tengo mucha' novia', mucha' novia'_x000D_
+Hoy tengo a una, mañana otra, ey, pero no hay boda_x000D_
+Tití me preguntó si tengo mucha' novia', je, mucha' novia'_x000D_
+Hoy tengo a una, mañana otra_x000D_
+_x000D_
+[Refrán: Bad Bunny]_x000D_
+Me la' vo'a llevar a to'a pa' un VIP, un VIP, ey_x000D_
+Saluden a Tití_x000D_
+Vamo' a tirarno' un selfie, say "cheese", ey_x000D_
+Que sonrían las que ya les metí_x000D_
+En un VIP, un VIP, ey_x000D_
+Saluden a Tití_x000D_
+Vamo' a tirarno' un selfie, say "cheese"_x000D_
+Que sonrían las que ya se olvidaron de mí_x000D_
+_x000D_
+[Verso 1: Bad Bunny]_x000D_
+Me gustan mucho las Gabriela_x000D_
+Las Patricia, las Nicole, las Sofía_x000D_
+Mi primera novia en kinder, María_x000D_
+Y mi primer amor se llamaba Thalía_x000D_
+Tengo una colombiana que mе escribe to' los día'_x000D_
+Y una mexicana quе ni yo sabía_x000D_
+Otra en San Antonio que me quiere todavía_x000D_
+Y las de PR que todita' son mía'_x000D_
+Una dominicana que es uva bombón_x000D_
+Uva, uva bombón_x000D_
+La de Barcelona que vino en avión_x000D_
+Y dice que mi bicho está cabrón_x000D_
+Yo dejo que jueguen con mi corazón_x000D_
+Quisiera mudarme con toda' pa' una mansión_x000D_
+El día que me case te envío la invitación_x000D_
+Muchacho, deja eso, ey_x000D_
+_x000D_
+[Coro: Bad Bunny]_x000D_
+Tití me preguntó si tengo mucha' novia', mucha' novia'_x000D_
+Hoy tengo una, mañana otra, ey, pero no hay boda_x000D_
+Tití me preguntó si tengo mucha' novia', ey, ey, mucha' novia'_x000D_
+Hoy tengo una, mañana otra (Mañana otra; ¡rra!)_x000D_
+_x000D_
+[Post-Coro: Bad Bunny &amp; Kiko El Crazy]_x000D_
+Tití me preguntó-tó-tó-tó-tó-tó-tó-tó_x000D_
+Tití me preguntó-tó-tó-tó-tó-tó-tó-tó (Qué pámpara)_x000D_
+Tití me preguntó-tó-tó-tó-tó-tó-tó-tó_x000D_
+Tití me preguntó-tó-tó-tó-tó (Pero ven acá, muchacho, ¿y para qué tú quiere' tanta' novia'?)_x000D_
+_x000D_
+[Refrán: Bad Bunny]_x000D_
+Me la' vo'a llevar a to'a pa' un VIP, un VIP, ey_x000D_
+Saluden a Tití_x000D_
+Vamo' a tirarno' un selfie, say "cheese", ey_x000D_
+Que sonrían las que ya les metí_x000D_
+En un VIP, un VIP, ey_x000D_
+Saluden a Tití_x000D_
+Vamo' a tirarno' un selfie, say "cheese"_x000D_
+Que sonrían las que ya se olvidaron de mí_x000D_
+_x000D_
+[Interludio]_x000D_
+Oye, muchacho 'el diablo azaroso_x000D_
+Suelta ese mal vivir que tú tiene' en la calle_x000D_
+Búscate una mujer seria pa' ti_x000D_
+Chacho 'el diablo, coño_x000D_
+[Puente: Bad Bunny]_x000D_
+Yo quisiera enamorarme_x000D_
+Pero no puedo, pero no puedo, eh, eh_x000D_
+Yo quisiera enamorarme_x000D_
+Pero no puedo, pero no puedo_x000D_
+_x000D_
+[Verso 2: Bad Bunny]_x000D_
+Sorry, yo no confío, yo no confío_x000D_
+Nah, ni en mí mismo confío_x000D_
+Si quiere' quedarte hoy que hace frío_x000D_
+Y mañana te va', nah_x000D_
+Muchas quieren mi baby gravy_x000D_
+Quieren tener mi primogénito, ey_x000D_
+Y llevarse el crédito_x000D_
+Ya me aburrí, hoy quiero un totito inédito, je_x000D_
+Uno nuevo, uno nuevo, uno nuevo, uno nuevo (Ey)_x000D_
+Hazle caso a tu amiga, ella tiene razón_x000D_
+Yo vo'a romperte el corazón, vo'a romperte el corazón_x000D_
+Ey, no te enamore' de mí (No, no)_x000D_
+No te enamore' de mí (No, no), ey_x000D_
+Sorry, yo soy así (Así, así), ey_x000D_
+No sé por qué soy así (Ey)_x000D_
+Hazle caso a tu amiga, ella tiene razón_x000D_
+Yo vo'a romperte el corazón, vo'a romperte el corazón (Ey, ey)_x000D_
+No te enamore' de mí (No)_x000D_
+No te enamore' de mí (No), no_x000D_
+Sorry, yo soy así_x000D_
+Ya no quiero ser así, no_x000D_
+[Outro Instrumental]_x000D_
+_x000D_
 </t>
   </si>
   <si>
@@ -22419,7 +22533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F240"/>
+  <dimension ref="A1:F241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
@@ -25355,19 +25469,19 @@
         <v>2019</v>
       </c>
       <c r="B148" t="s">
-        <v>349</v>
+        <v>524</v>
       </c>
       <c r="C148" t="s">
-        <v>202</v>
+        <v>525</v>
       </c>
       <c r="D148" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E148" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F148" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -25375,7 +25489,7 @@
         <v>2019</v>
       </c>
       <c r="B149" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C149" t="s">
         <v>209</v>
@@ -25384,10 +25498,10 @@
         <v>44</v>
       </c>
       <c r="E149" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F149" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -25395,7 +25509,7 @@
         <v>2019</v>
       </c>
       <c r="B150" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C150" t="s">
         <v>209</v>
@@ -25404,10 +25518,10 @@
         <v>44</v>
       </c>
       <c r="E150" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="F150" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -25415,19 +25529,19 @@
         <v>2019</v>
       </c>
       <c r="B151" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C151" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="D151" t="s">
         <v>44</v>
       </c>
       <c r="E151" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="F151" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -25435,19 +25549,19 @@
         <v>2020</v>
       </c>
       <c r="B152" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C152" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D152" t="s">
         <v>44</v>
       </c>
       <c r="E152" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="F152" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -25455,19 +25569,19 @@
         <v>2020</v>
       </c>
       <c r="B153" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C153" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="D153" t="s">
         <v>8</v>
       </c>
       <c r="E153" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="F153" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -25475,19 +25589,19 @@
         <v>2020</v>
       </c>
       <c r="B154" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C154" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="D154" t="s">
         <v>8</v>
       </c>
       <c r="E154" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="F154" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -25495,19 +25609,19 @@
         <v>2020</v>
       </c>
       <c r="B155" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C155" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D155" t="s">
         <v>8</v>
       </c>
       <c r="E155" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="F155" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -25515,7 +25629,7 @@
         <v>2020</v>
       </c>
       <c r="B156" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C156" t="s">
         <v>202</v>
@@ -25524,10 +25638,10 @@
         <v>44</v>
       </c>
       <c r="E156" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F156" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -25535,19 +25649,19 @@
         <v>2020</v>
       </c>
       <c r="B157" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C157" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="D157" t="s">
         <v>8</v>
       </c>
       <c r="E157" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F157" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="158" spans="1:6">
@@ -25555,19 +25669,19 @@
         <v>2020</v>
       </c>
       <c r="B158" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C158" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="D158" t="s">
         <v>8</v>
       </c>
       <c r="E158" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F158" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -25575,19 +25689,19 @@
         <v>2020</v>
       </c>
       <c r="B159" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C159" t="s">
-        <v>390</v>
+        <v>566</v>
       </c>
       <c r="D159" t="s">
         <v>8</v>
       </c>
       <c r="E159" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="F159" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -25595,19 +25709,19 @@
         <v>2020</v>
       </c>
       <c r="B160" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="C160" t="s">
-        <v>567</v>
+        <v>390</v>
       </c>
       <c r="D160" t="s">
         <v>8</v>
       </c>
       <c r="E160" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="F160" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -25615,19 +25729,19 @@
         <v>2020</v>
       </c>
       <c r="B161" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="C161" t="s">
-        <v>202</v>
+        <v>573</v>
       </c>
       <c r="D161" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E161" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="F161" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -25635,19 +25749,19 @@
         <v>2020</v>
       </c>
       <c r="B162" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="C162" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="D162" t="s">
         <v>44</v>
       </c>
       <c r="E162" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="F162" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -25655,19 +25769,19 @@
         <v>2020</v>
       </c>
       <c r="B163" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="C163" t="s">
-        <v>577</v>
+        <v>209</v>
       </c>
       <c r="D163" t="s">
         <v>44</v>
       </c>
       <c r="E163" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F163" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -25675,19 +25789,19 @@
         <v>2020</v>
       </c>
       <c r="B164" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C164" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="D164" t="s">
         <v>44</v>
       </c>
       <c r="E164" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="F164" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -25695,39 +25809,39 @@
         <v>2020</v>
       </c>
       <c r="B165" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C165" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="D165" t="s">
         <v>44</v>
       </c>
       <c r="E165" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="F165" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
     </row>
     <row r="166" spans="1:6">
       <c r="A166">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B166" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C166" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="D166" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E166" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F166" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -25735,19 +25849,19 @@
         <v>2021</v>
       </c>
       <c r="B167" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C167" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D167" t="s">
         <v>8</v>
       </c>
       <c r="E167" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F167" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -25755,19 +25869,19 @@
         <v>2021</v>
       </c>
       <c r="B168" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C168" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D168" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E168" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="F168" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -25775,19 +25889,19 @@
         <v>2021</v>
       </c>
       <c r="B169" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C169" t="s">
-        <v>549</v>
+        <v>603</v>
       </c>
       <c r="D169" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E169" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="F169" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -25795,19 +25909,19 @@
         <v>2021</v>
       </c>
       <c r="B170" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C170" t="s">
-        <v>604</v>
+        <v>551</v>
       </c>
       <c r="D170" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E170" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="F170" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -25815,19 +25929,19 @@
         <v>2021</v>
       </c>
       <c r="B171" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="C171" t="s">
-        <v>354</v>
+        <v>610</v>
       </c>
       <c r="D171" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E171" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="F171" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -25835,19 +25949,19 @@
         <v>2021</v>
       </c>
       <c r="B172" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="C172" t="s">
-        <v>611</v>
+        <v>354</v>
       </c>
       <c r="D172" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E172" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="F172" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -25855,19 +25969,19 @@
         <v>2021</v>
       </c>
       <c r="B173" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C173" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="D173" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E173" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F173" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -25875,19 +25989,19 @@
         <v>2021</v>
       </c>
       <c r="B174" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C174" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D174" t="s">
         <v>8</v>
       </c>
       <c r="E174" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F174" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -25895,19 +26009,19 @@
         <v>2021</v>
       </c>
       <c r="B175" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C175" t="s">
-        <v>7</v>
+        <v>625</v>
       </c>
       <c r="D175" t="s">
         <v>8</v>
       </c>
       <c r="E175" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="F175" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -25915,19 +26029,19 @@
         <v>2021</v>
       </c>
       <c r="B176" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C176" t="s">
-        <v>202</v>
+        <v>7</v>
       </c>
       <c r="D176" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E176" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F176" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -25935,19 +26049,19 @@
         <v>2021</v>
       </c>
       <c r="B177" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="C177" t="s">
-        <v>629</v>
+        <v>202</v>
       </c>
       <c r="D177" t="s">
         <v>44</v>
       </c>
       <c r="E177" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="F177" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -25955,19 +26069,19 @@
         <v>2021</v>
       </c>
       <c r="B178" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C178" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D178" t="s">
         <v>44</v>
       </c>
       <c r="E178" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="F178" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -25975,19 +26089,19 @@
         <v>2021</v>
       </c>
       <c r="B179" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C179" t="s">
-        <v>209</v>
+        <v>639</v>
       </c>
       <c r="D179" t="s">
         <v>44</v>
       </c>
       <c r="E179" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="F179" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -25995,39 +26109,39 @@
         <v>2021</v>
       </c>
       <c r="B180" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C180" t="s">
-        <v>640</v>
+        <v>209</v>
       </c>
       <c r="D180" t="s">
         <v>44</v>
       </c>
       <c r="E180" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="F180" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="181" spans="1:6">
       <c r="A181">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B181" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C181" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="D181" t="s">
-        <v>8</v>
+        <v>647</v>
       </c>
       <c r="E181" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="F181" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -26035,19 +26149,19 @@
         <v>2022</v>
       </c>
       <c r="B182" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="C182" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="D182" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E182" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="F182" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -26055,19 +26169,19 @@
         <v>2022</v>
       </c>
       <c r="B183" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C183" t="s">
-        <v>549</v>
+        <v>655</v>
       </c>
       <c r="D183" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E183" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="F183" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -26075,19 +26189,19 @@
         <v>2022</v>
       </c>
       <c r="B184" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C184" t="s">
-        <v>202</v>
+        <v>551</v>
       </c>
       <c r="D184" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E184" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="F184" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -26095,19 +26209,19 @@
         <v>2022</v>
       </c>
       <c r="B185" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C185" t="s">
-        <v>589</v>
+        <v>202</v>
       </c>
       <c r="D185" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E185" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="F185" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -26115,19 +26229,19 @@
         <v>2022</v>
       </c>
       <c r="B186" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="C186" t="s">
-        <v>661</v>
+        <v>595</v>
       </c>
       <c r="D186" t="s">
         <v>8</v>
       </c>
       <c r="E186" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F186" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -26135,19 +26249,19 @@
         <v>2022</v>
       </c>
       <c r="B187" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="C187" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="D187" t="s">
         <v>8</v>
       </c>
       <c r="E187" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="F187" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -26155,19 +26269,19 @@
         <v>2022</v>
       </c>
       <c r="B188" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="C188" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D188" t="s">
         <v>8</v>
       </c>
       <c r="E188" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="F188" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -26175,19 +26289,19 @@
         <v>2022</v>
       </c>
       <c r="B189" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C189" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D189" t="s">
         <v>8</v>
       </c>
       <c r="E189" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="F189" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -26195,19 +26309,19 @@
         <v>2022</v>
       </c>
       <c r="B190" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="C190" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="D190" t="s">
         <v>8</v>
       </c>
       <c r="E190" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="F190" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -26215,19 +26329,19 @@
         <v>2022</v>
       </c>
       <c r="B191" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="C191" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="D191" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E191" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="F191" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -26235,19 +26349,19 @@
         <v>2022</v>
       </c>
       <c r="B192" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="C192" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="D192" t="s">
         <v>44</v>
       </c>
       <c r="E192" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="F192" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -26255,19 +26369,19 @@
         <v>2022</v>
       </c>
       <c r="B193" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C193" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="D193" t="s">
         <v>44</v>
       </c>
       <c r="E193" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="F193" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -26275,19 +26389,19 @@
         <v>2022</v>
       </c>
       <c r="B194" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C194" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="D194" t="s">
         <v>44</v>
       </c>
       <c r="E194" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="F194" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="195" spans="1:6">
@@ -26295,39 +26409,39 @@
         <v>2022</v>
       </c>
       <c r="B195" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="C195" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="D195" t="s">
         <v>44</v>
       </c>
       <c r="E195" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="F195" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="196" spans="1:6">
       <c r="A196">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B196" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C196" t="s">
-        <v>700</v>
+        <v>551</v>
       </c>
       <c r="D196" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E196" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="F196" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -26335,19 +26449,19 @@
         <v>2023</v>
       </c>
       <c r="B197" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="C197" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="D197" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E197" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="F197" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -26355,19 +26469,19 @@
         <v>2023</v>
       </c>
       <c r="B198" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="C198" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="D198" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E198" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="F198" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -26375,19 +26489,19 @@
         <v>2023</v>
       </c>
       <c r="B199" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="C199" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="D199" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E199" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="F199" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -26395,19 +26509,19 @@
         <v>2023</v>
       </c>
       <c r="B200" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="C200" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="D200" t="s">
         <v>8</v>
       </c>
       <c r="E200" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="F200" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -26415,19 +26529,19 @@
         <v>2023</v>
       </c>
       <c r="B201" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C201" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="D201" t="s">
         <v>8</v>
       </c>
       <c r="E201" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="F201" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -26435,19 +26549,19 @@
         <v>2023</v>
       </c>
       <c r="B202" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C202" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="D202" t="s">
         <v>8</v>
       </c>
       <c r="E202" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="F202" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -26455,19 +26569,19 @@
         <v>2023</v>
       </c>
       <c r="B203" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C203" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="D203" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E203" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="F203" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -26475,19 +26589,19 @@
         <v>2023</v>
       </c>
       <c r="B204" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="C204" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="D204" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E204" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="F204" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -26495,19 +26609,19 @@
         <v>2023</v>
       </c>
       <c r="B205" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
       <c r="C205" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="D205" t="s">
         <v>8</v>
       </c>
       <c r="E205" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="F205" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -26515,19 +26629,19 @@
         <v>2023</v>
       </c>
       <c r="B206" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="C206" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="D206" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E206" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="F206" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -26535,19 +26649,19 @@
         <v>2023</v>
       </c>
       <c r="B207" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="C207" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D207" t="s">
         <v>44</v>
       </c>
       <c r="E207" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="F207" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -26555,19 +26669,19 @@
         <v>2023</v>
       </c>
       <c r="B208" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C208" t="s">
-        <v>202</v>
+        <v>751</v>
       </c>
       <c r="D208" t="s">
         <v>44</v>
       </c>
       <c r="E208" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="F208" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -26575,7 +26689,7 @@
         <v>2023</v>
       </c>
       <c r="B209" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="C209" t="s">
         <v>202</v>
@@ -26584,10 +26698,10 @@
         <v>44</v>
       </c>
       <c r="E209" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="F209" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
     <row r="210" spans="1:6">
@@ -26595,39 +26709,39 @@
         <v>2023</v>
       </c>
       <c r="B210" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="C210" t="s">
-        <v>689</v>
+        <v>202</v>
       </c>
       <c r="D210" t="s">
         <v>44</v>
       </c>
       <c r="E210" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="F210" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
     </row>
     <row r="211" spans="1:6">
       <c r="A211">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B211" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="C211" t="s">
-        <v>757</v>
+        <v>696</v>
       </c>
       <c r="D211" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="E211" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="F211" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
     </row>
     <row r="212" spans="1:6">
@@ -26635,19 +26749,19 @@
         <v>2024</v>
       </c>
       <c r="B212" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="C212" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="D212" t="s">
         <v>8</v>
       </c>
       <c r="E212" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="F212" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
     </row>
     <row r="213" spans="1:6">
@@ -26655,19 +26769,19 @@
         <v>2024</v>
       </c>
       <c r="B213" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C213" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="D213" t="s">
         <v>8</v>
       </c>
       <c r="E213" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="F213" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="214" spans="1:6">
@@ -26675,19 +26789,19 @@
         <v>2024</v>
       </c>
       <c r="B214" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C214" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="D214" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E214" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="F214" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
     </row>
     <row r="215" spans="1:6">
@@ -26695,19 +26809,19 @@
         <v>2024</v>
       </c>
       <c r="B215" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C215" t="s">
-        <v>712</v>
+        <v>776</v>
       </c>
       <c r="D215" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E215" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="F215" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
     </row>
     <row r="216" spans="1:6">
@@ -26715,19 +26829,19 @@
         <v>2024</v>
       </c>
       <c r="B216" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="C216" t="s">
-        <v>776</v>
+        <v>719</v>
       </c>
       <c r="D216" t="s">
         <v>8</v>
       </c>
       <c r="E216" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="F216" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
     </row>
     <row r="217" spans="1:6">
@@ -26735,19 +26849,19 @@
         <v>2024</v>
       </c>
       <c r="B217" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="C217" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="D217" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E217" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="F217" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
     </row>
     <row r="218" spans="1:6">
@@ -26755,19 +26869,19 @@
         <v>2024</v>
       </c>
       <c r="B218" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C218" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="D218" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E218" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="F218" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
     </row>
     <row r="219" spans="1:6">
@@ -26775,19 +26889,19 @@
         <v>2024</v>
       </c>
       <c r="B219" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C219" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="D219" t="s">
         <v>8</v>
       </c>
       <c r="E219" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="F219" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
     </row>
     <row r="220" spans="1:6">
@@ -26795,19 +26909,19 @@
         <v>2024</v>
       </c>
       <c r="B220" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C220" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="D220" t="s">
         <v>8</v>
       </c>
       <c r="E220" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="F220" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
     </row>
     <row r="221" spans="1:6">
@@ -26815,19 +26929,19 @@
         <v>2024</v>
       </c>
       <c r="B221" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="C221" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="D221" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="E221" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
       <c r="F221" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
     </row>
     <row r="222" spans="1:6">
@@ -26835,19 +26949,19 @@
         <v>2024</v>
       </c>
       <c r="B222" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C222" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="D222" t="s">
         <v>44</v>
       </c>
       <c r="E222" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="F222" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
     </row>
     <row r="223" spans="1:6">
@@ -26855,19 +26969,19 @@
         <v>2024</v>
       </c>
       <c r="B223" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="C223" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="D223" t="s">
         <v>44</v>
       </c>
       <c r="E223" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="F223" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
     </row>
     <row r="224" spans="1:6">
@@ -26875,19 +26989,19 @@
         <v>2024</v>
       </c>
       <c r="B224" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="C224" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="D224" t="s">
         <v>44</v>
       </c>
       <c r="E224" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="F224" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="225" spans="1:6">
@@ -26895,39 +27009,39 @@
         <v>2024</v>
       </c>
       <c r="B225" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="C225" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="D225" t="s">
         <v>44</v>
       </c>
       <c r="E225" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="F225" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="226" spans="1:6">
       <c r="A226">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B226" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C226" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="D226" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="E226" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="F226" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="227" spans="1:6">
@@ -26935,19 +27049,19 @@
         <v>2025</v>
       </c>
       <c r="B227" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="C227" t="s">
-        <v>549</v>
+        <v>822</v>
       </c>
       <c r="D227" t="s">
-        <v>8</v>
+        <v>118</v>
       </c>
       <c r="E227" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="F227" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
     </row>
     <row r="228" spans="1:6">
@@ -26955,19 +27069,19 @@
         <v>2025</v>
       </c>
       <c r="B228" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="C228" t="s">
-        <v>822</v>
+        <v>551</v>
       </c>
       <c r="D228" t="s">
         <v>8</v>
       </c>
       <c r="E228" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="F228" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
     </row>
     <row r="229" spans="1:6">
@@ -26975,19 +27089,19 @@
         <v>2025</v>
       </c>
       <c r="B229" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="C229" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D229" t="s">
         <v>8</v>
       </c>
       <c r="E229" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="F229" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
     </row>
     <row r="230" spans="1:6">
@@ -26995,19 +27109,19 @@
         <v>2025</v>
       </c>
       <c r="B230" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="C230" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D230" t="s">
         <v>8</v>
       </c>
       <c r="E230" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="F230" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
     </row>
     <row r="231" spans="1:6">
@@ -27015,19 +27129,19 @@
         <v>2025</v>
       </c>
       <c r="B231" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="C231" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D231" t="s">
         <v>8</v>
       </c>
       <c r="E231" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="F231" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
     </row>
     <row r="232" spans="1:6">
@@ -27035,19 +27149,19 @@
         <v>2025</v>
       </c>
       <c r="B232" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
       <c r="C232" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D232" t="s">
         <v>8</v>
       </c>
       <c r="E232" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="F232" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
     </row>
     <row r="233" spans="1:6">
@@ -27055,19 +27169,19 @@
         <v>2025</v>
       </c>
       <c r="B233" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C233" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D233" t="s">
         <v>8</v>
       </c>
       <c r="E233" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="F233" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
     </row>
     <row r="234" spans="1:6">
@@ -27075,19 +27189,19 @@
         <v>2025</v>
       </c>
       <c r="B234" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="C234" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D234" t="s">
         <v>8</v>
       </c>
       <c r="E234" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="F234" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
     </row>
     <row r="235" spans="1:6">
@@ -27095,19 +27209,19 @@
         <v>2025</v>
       </c>
       <c r="B235" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="C235" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D235" t="s">
-        <v>118</v>
+        <v>8</v>
       </c>
       <c r="E235" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="F235" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
     </row>
     <row r="236" spans="1:6">
@@ -27115,19 +27229,19 @@
         <v>2025</v>
       </c>
       <c r="B236" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="C236" t="s">
-        <v>202</v>
+        <v>857</v>
       </c>
       <c r="D236" t="s">
-        <v>44</v>
+        <v>118</v>
       </c>
       <c r="E236" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="F236" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
     </row>
     <row r="237" spans="1:6">
@@ -27135,19 +27249,19 @@
         <v>2025</v>
       </c>
       <c r="B237" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="C237" t="s">
-        <v>796</v>
+        <v>202</v>
       </c>
       <c r="D237" t="s">
         <v>44</v>
       </c>
       <c r="E237" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="F237" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
     </row>
     <row r="238" spans="1:6">
@@ -27155,19 +27269,19 @@
         <v>2025</v>
       </c>
       <c r="B238" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C238" t="s">
-        <v>43</v>
+        <v>803</v>
       </c>
       <c r="D238" t="s">
         <v>44</v>
       </c>
       <c r="E238" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="F238" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
     <row r="239" spans="1:6">
@@ -27175,19 +27289,19 @@
         <v>2025</v>
       </c>
       <c r="B239" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="C239" t="s">
-        <v>689</v>
+        <v>43</v>
       </c>
       <c r="D239" t="s">
         <v>44</v>
       </c>
       <c r="E239" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="F239" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
     </row>
     <row r="240" spans="1:6">
@@ -27195,19 +27309,39 @@
         <v>2025</v>
       </c>
       <c r="B240" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="C240" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="D240" t="s">
         <v>44</v>
       </c>
       <c r="E240" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="F240" t="s">
-        <v>867</v>
+        <v>871</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
+      <c r="A241">
+        <v>2025</v>
+      </c>
+      <c r="B241" t="s">
+        <v>872</v>
+      </c>
+      <c r="C241" t="s">
+        <v>696</v>
+      </c>
+      <c r="D241" t="s">
+        <v>44</v>
+      </c>
+      <c r="E241" t="s">
+        <v>873</v>
+      </c>
+      <c r="F241" t="s">
+        <v>874</v>
       </c>
     </row>
   </sheetData>
